--- a/demo/sample_report_pptx_검토후보.xlsx
+++ b/demo/sample_report_pptx_검토후보.xlsx
@@ -9,15 +9,22 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검토 목록" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보류" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외 페이지" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이미지 페이지" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실행 정보" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외 문장" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="페이지" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경 사항" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외 페이지" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이미지 페이지" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실행 정보" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토 목록'!$A$1:$G$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'제외 페이지'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'이미지 페이지'!$A$1:$C$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'실행 정보'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토 목록'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보류'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'제외 문장'!$A$1:$M$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'페이지'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'변경 사항'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'제외 페이지'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'이미지 페이지'!$A$1:$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'실행 정보'!$A$1:$B$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +46,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,16 @@
         <fgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,13 +101,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -100,6 +120,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -467,16 +490,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,22 +526,52 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>줄</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>발췌</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>논의 포인트</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>점수</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
@@ -528,22 +587,38 @@
       <c r="C2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>고온(85℃ 이상) 환경에서 출력 오프셋이 시간에 따라 변하는 드리프트 현상 발생</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -557,22 +632,38 @@
       <c r="C3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2분기 필드 불량률 1.8%로 목표 0.5% 대비 초과</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -586,22 +677,38 @@
       <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>기존 보정 방식은 상온 1점 캘리브레이션만 수행하여 온도 변화 대응 불가</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -615,26 +722,38 @@
       <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>다이 어태치 접착제(에폭시계)와 세라믹 기판의 열팽창계수 차이로 고온에서 다이에 응력 발생</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>보정(A→C)</t>
-        </is>
-      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -648,26 +767,38 @@
       <c r="C6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>응력이 피에조 저항 브리지의 불균형을 유발하여 오프셋 변화로 나타남</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>보정(A→C)</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -681,26 +812,38 @@
       <c r="C7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>접착제 두께 편차(±15㎛)가 클수록 드리프트가 커지는 경향 확인</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>보정(A→C)</t>
-        </is>
-      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -714,22 +857,42 @@
       <c r="C8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.02)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -743,22 +906,42 @@
       <c r="C9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>접착제를 저탄성 실리콘계로 변경하여 다이로 전달되는 응력 저감</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>분류기 A(0.01)</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -772,22 +955,38 @@
       <c r="C10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>다이 하부에 응력 완충용 더미 층(폴리이미드 25㎛) 삽입</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -801,22 +1000,42 @@
       <c r="C11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>접착제 도포량 자동 제어로 두께 편차 ±5㎛ 이내 관리</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.00), 불일치</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -830,22 +1049,38 @@
       <c r="C12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>펌웨어에서 온도별 오프셋을 2차 다항식으로 보정</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -859,22 +1094,42 @@
       <c r="C13" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>캘리브레이션 포인트를 1점(25℃)에서 3점(-20/25/85℃)으로 확대</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>분류기 A(0.03)</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -888,22 +1143,38 @@
       <c r="C14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>보정 계수는 모듈별로 OTP 메모리에 저장하고 부팅 시 로드</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -917,22 +1188,38 @@
       <c r="C15" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>연산량 증가는 기존 MCU 사이클 내에서 수용 가능</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -946,22 +1233,42 @@
       <c r="C16" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>85℃ 500시간 시험에서 오프셋 드리프트 0.35%FS → 0.10%FS (약 70% 감소)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>분류기 A(0.04), 불일치</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -975,22 +1282,38 @@
       <c r="C17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>조립 수율 92.1% → 97.8%로 향상</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1004,22 +1327,42 @@
       <c r="C18" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>응답 시간은 1.2ms로 변화 없음</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>분류기 B(0.05)</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1033,22 +1376,42 @@
       <c r="C19" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>두 개선안을 모두 적용한 조건의 결과이며 개별 기여도는 별도 분석 예정</t>
+      <c r="D19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>항목: 오프셋 드리프트 | 개선 전: 0.35 %FS | 개선 후: 0.10 %FS</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>표, 분류기 B(0.04)</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1062,26 +1425,42 @@
       <c r="C20" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>항목: 오프셋 드리프트 | 개선 전: 0.35 %FS | 개선 후: 0.10 %FS</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>항목: 조립 수율 | 개선 전: 92.1 % | 개선 후: 97.8 %</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>표</t>
         </is>
       </c>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1089,32 +1468,44 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>검증 결과</t>
+          <t>추가 검토 사항</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>항목: 조립 수율 | 개선 전: 92.1 % | 개선 후: 97.8 %</t>
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
+          <t>전원 노이즈가 큰 일부 고객 설비에서 간헐적 출력 스파이크 관측</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>표</t>
-        </is>
-      </c>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1128,22 +1519,38 @@
       <c r="C22" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>전원 노이즈가 큰 일부 고객 설비에서 간헐적 출력 스파이크 관측</t>
+      <c r="D22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>입력단 필터 구조 변경(RC → LC) 검토 예정</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>변경 내용의 구체적 구성은 무엇인가.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1157,22 +1564,38 @@
       <c r="C23" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>입력단 필터 구조 변경(RC → LC) 검토 예정</t>
+      <c r="D23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>변경 내용의 구체적 구성은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>경쟁사 B 제품 대비 응답 속도 우위(1.2ms vs 2.0ms)는 유지 확인</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1180,28 +1603,44 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>추가 검토 사항</t>
+          <t>향후 계획</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>경쟁사 B 제품 대비 응답 속도 우위(1.2ms vs 2.0ms)는 유지 확인</t>
+        <v>11</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>차기 모델 PS-300에 자체 개발 온도 보정 IP 적용 예정</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>변경 내용의 구체적 구성은 무엇인가.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1215,54 +1654,46 @@
       <c r="C25" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>차기 모델 PS-300에 자체 개발 온도 보정 IP 적용 예정</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
+          <t>생산 데이터 기반 AI 이상 감지 도입 검토</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>변경 내용의 구체적 구성은 무엇인가.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>향후 계획</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>생산 데이터 기반 AI 이상 감지 도입 검토</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>변경 내용의 구체적 구성은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G26"/>
+  <autoFilter ref="A1:M25"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L2:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+      <formula1>"O,X,A,B,C,D"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1273,16 +1704,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1303,31 +1741,1617 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>줄</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>발췌</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>논의 포인트</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>점수</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>보류 사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>검증 결과</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>X?</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>두 개선안을 모두 적용한 조건의 결과이며 개별 기여도는 별도 분석 예정</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>모델은 제외로 보았으나 기술 단서어가 있음. 포함 여부 확인.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>분류기 X(0.03), 단서어: 개선, 조건</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>모델은 제외, 기술 단서어 있음</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N2"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+      <formula1>"O,X,A,B,C,D"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>섹션</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>페이지</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>줄</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>발췌</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>논의 포인트</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>점수</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>배경 및 문제점</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>향후 계획</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>사내 조립 공정 표준 개정 추진</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M3"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L2:L3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+      <formula1>"O,X,A,B,C,D"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>페이지</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>가중치 근거</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>문장</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>제목 출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PS-200 압력 센서 모듈 고온 드리프트 개선 결과 보고</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>유형 result+means</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>표지</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>목차</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>제목 규칙: '목차'</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>배경 및 문제점</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>유형 problem</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>원인 분석</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>유형 problem</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>개선안 1: 패키지 접착 구조 변경</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>means</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>유형 means</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>개선안 2: 온도 보상 알고리즘</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>means</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>유형 means</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>개선 전후 구조 비교</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>유형 result+means</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>이미지 페이지</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>검증 결과</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>유형 result</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>추가 검토 사항</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>유형 plan</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>양산 적용 일정 및 비용</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>means</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>유형 means</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>제목 규칙: '일정'</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>향후 계획</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>유형 plan</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>감사합니다</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>기본값</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>제목 규칙: '감사합니다'</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>페이지</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>줄</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>발췌</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>이전</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>현재</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>직전 실행 20261027-194955-samplereport 과 비교 (현재 20261027-195017-samplereport)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>판정 모드: llm → hybrid</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>분류기: - → 제로샷(원형 문장)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>목록 진입</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>응답 시간은 1.2ms로 변화 없음</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>이전 실행에서는 목록에 없었음 (이전 X)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>목록 이탈</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>이전 C → 현재 X</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>목록 이탈</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>사내 조립 공정 표준 개정 추진</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>이전 C → 현재 X</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>등급 변경</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>B → C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>등급 변경</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>연산량 증가는 기존 MCU 사이클 내에서 수용 가능</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>A → B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>응력이 피에조 저항 브리지의 불균형을 유발하여 오프셋 변화로 나타남</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.72 → 0.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>접착제 두께 편차(±15㎛)가 클수록 드리프트가 커지는 경향 확인</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.72 → 0.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>다이 하부에 응력 완충용 더미 층(폴리이미드 25㎛) 삽입</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>접착제 도포량 자동 제어로 두께 편차 ±5㎛ 이내 관리</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>펌웨어에서 온도별 오프셋을 2차 다항식으로 보정</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>보정 계수는 모듈별로 OTP 메모리에 저장하고 부팅 시 로드</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>85℃ 500시간 시험에서 오프셋 드리프트 0.35%FS → 0.10%FS (약 70% 감소)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.81 → 0.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>항목: 조립 수율 | 개선 전: 92.1 % | 개선 후: 97.8 %</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.81 → 0.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>차기 모델 PS-300에 자체 개발 온도 보정 IP 적용 예정</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.68 → 0.53</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1424,7 +3448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1476,17 +3500,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1516,103 +3540,111 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>실행 ID</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>qwen3:4b-instruct</t>
+          <t>20261027-195017-samplereport</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>프롬프트 버전</t>
+          <t>직전 실행 ID</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>v3-2026-10-26</t>
+          <t>20261027-194955-samplereport</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>시작</t>
+          <t>판정 모드</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26T01:55:29</t>
+          <t>hybrid</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>소요 시간(초)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>7.3</v>
+          <t>LLM 모델</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>qwen3:4b-instruct</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>페이지 수</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>12</v>
+          <t>프롬프트 버전</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>v5-2026-10-27</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>라벨링 페이지</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>7</v>
+          <t>임베딩 모델</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>bge-m3</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>제외 페이지</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>4</v>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>제로샷(원형 문장)</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>이미지 페이지</t>
+          <t>확신 임계값</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LLM 호출</t>
+          <t>목록 점수 기준</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>캐시 적중</t>
+          <t>점수 미달 보류</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1622,41 +3654,223 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>등급 분포</t>
+          <t>LLM 재확인 문장</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>A: 7, B: 9, C: 6, D: 3, X: 2, X?: 0, ?: 0</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>전처리로 제거된 줄</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>숫자만: 1, 반복 문구: 12, 일정/금액: 3, 담당자: 1, 짧은 조각: 1</t>
-        </is>
+          <t>분류기 채택 문장</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>LLM 판정 문장</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>임베딩 시간(초)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LLM 시간(초)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>시작</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27T19:50:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>소요 시간(초)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>페이지 수</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>라벨링 페이지</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>제외 페이지</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>이미지 페이지</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LLM 호출</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>캐시 적중</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>검토 목록</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>A: 6, B: 8, C: 7, D: 3 (합 24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>등급 분포(전체)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>A: 6, B: 8, C: 7, D: 3, X: 2, X?: 1, ?: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>직전 실행 대비</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>entered: 1, left: 2, grade: 2, score: 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>달라진 설정</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>판정 모드: llm → hybrid; 분류기: - → 제로샷(원형 문장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>전처리로 제거된 줄</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>숫자만: 1, 반복 문구: 12, 일정/금액: 3, 담당자: 1, 짧은 조각: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>경고</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>피드백 방법</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>검토 목록·보류·제외 문장 시트의 '피드백' 열에 O=맞음, X=틀림(제외), A/B/C/D=올바른 등급. 저장 후 UI '정확도 관리 → 피드백 가져오기' 또는 ip-finder feedback &lt;이 파일&gt;</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
+  <autoFilter ref="A1:B32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demo/sample_report_pptx_검토후보.xlsx
+++ b/demo/sample_report_pptx_검토후보.xlsx
@@ -9,22 +9,24 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검토 목록" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보류" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외 문장" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 제외" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="페이지" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경 사항" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외 페이지" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이미지 페이지" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실행 정보" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1차 제외 (참고)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실행 정보" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토 목록'!$A$1:$M$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보류'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'제외 문장'!$A$1:$M$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'페이지'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'변경 사항'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토 목록'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보류'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2차 제외'!$A$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'페이지'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'변경 사항'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'제외 페이지'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'이미지 페이지'!$A$1:$C$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'실행 정보'!$A$1:$B$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'1차 제외 (참고)'!$A$1:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'실행 정보'!$A$1:$B$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -498,14 +500,16 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="64" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,20 +560,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>1차 분류기</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2차 LLM</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -606,19 +620,33 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.636</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.14)</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -651,19 +679,33 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.641</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr"/>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>분류기 B(0.15)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -696,19 +738,33 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.31)</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -741,19 +797,33 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.669</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.19)</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -786,19 +856,33 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.586</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.08)</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -831,19 +915,33 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.06)</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -860,39 +958,49 @@
       <c r="D8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>분류기 C(0.02)</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.02), 불일치</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -932,16 +1040,26 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>분류기 A(0.01)</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -974,19 +1092,33 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>분류기 A(0.08)</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1026,16 +1158,26 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>분류기 C(0.00), 불일치</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1068,19 +1210,33 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.742</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>분류기 A(0.09)</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1120,16 +1276,26 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>분류기 A(0.03)</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1162,19 +1328,33 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.743</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>분류기 A(0.09)</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1207,19 +1387,33 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>분류기 B(0.06)</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1252,23 +1446,33 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.585</v>
+        <v>0.65</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>분류기 A(0.04), 불일치</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1301,19 +1505,33 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.716</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>분류기 B(0.15)</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1346,23 +1564,33 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>분류기 B(0.05)</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1395,23 +1623,33 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>표, 분류기 B(0.04)</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1444,23 +1682,33 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>표</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr"/>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>표, 분류기 B(0.11)</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1493,19 +1741,33 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.605</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>분류기 C(0.16)</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1538,19 +1800,33 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>분류기 D(0.16)</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1583,19 +1859,33 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.583</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr"/>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>분류기 B(0.13)</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1628,19 +1918,33 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.527</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>분류기 D(0.05)</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1673,24 +1977,38 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>분류기 D(0.20)</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M25"/>
+  <autoFilter ref="A1:O25"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+    <dataValidation sqref="N2:N25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
       <formula1>"O,X,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1704,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1712,15 +2030,17 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="64" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1771,25 +2091,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>1차 분류기</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2차 LLM</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>보류 사유</t>
         </is>
@@ -1826,33 +2156,43 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.678</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>분류기 X(0.03), 단서어: 개선, 조건</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>단서어: 개선, 조건</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>모델은 제외, 기술 단서어 있음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:P2"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+    <dataValidation sqref="N2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
       <formula1>"O,X,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1866,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1874,14 +2214,16 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="64" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1932,111 +2274,60 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>1차 분류기</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2차 LLM</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>배경 및 문제점</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>향후 계획</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>사내 조립 공정 표준 개정 추진</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr"/>
+          <t>분류기 1차에서 뽑힌 문장 중 LLM 2차가 제외한 문장이 없습니다.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M3"/>
+  <autoFilter ref="A1:O2"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+    <dataValidation sqref="N2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
       <formula1>"O,X,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2050,19 +2341,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2078,7 +2371,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>유형</t>
+          <t>관련성</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -2088,7 +2381,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>가중치 근거</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -2112,6 +2405,16 @@
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>1차 제외</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2차 제외</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>제목 출처</t>
         </is>
@@ -2128,7 +2431,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -2136,7 +2439,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>유형 result+means</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -2153,7 +2456,13 @@
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2170,15 +2479,15 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>기본값</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2195,7 +2504,13 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2212,15 +2527,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>유형 problem</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2237,7 +2552,13 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2254,15 +2575,15 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>유형 problem</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2279,7 +2600,13 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2296,7 +2623,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>means</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -2304,7 +2631,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>유형 means</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2321,7 +2648,13 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2338,7 +2671,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>means</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -2346,7 +2679,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>유형 means</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2363,7 +2696,13 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2380,7 +2719,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -2388,7 +2727,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>유형 result+means</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2405,7 +2744,13 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2422,15 +2767,15 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>유형 result</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2447,7 +2792,13 @@
       <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2464,15 +2815,15 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>plan</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>유형 plan</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2489,7 +2840,13 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2506,7 +2863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>means</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -2514,7 +2871,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>유형 means</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2531,7 +2888,13 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2548,15 +2911,15 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>plan</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>유형 plan</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2573,7 +2936,13 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -2590,15 +2959,15 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>기본값</t>
+          <t>기본(높음)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2615,14 +2984,20 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:L13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2633,7 +3008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2704,7 +3079,7 @@
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>직전 실행 20261027-194955-samplereport 과 비교 (현재 20261027-195017-samplereport)</t>
+          <t>직전 실행 20261027-205722-samplereport 과 비교 (현재 20261027-205729-samplereport)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -2723,7 +3098,7 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>판정 모드: llm → hybrid</t>
+          <t>페이지 가중치 적용: 끔 → 켬</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -2733,16 +3108,12 @@
       <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>분류기: - → 제로샷(원형 문장)</t>
+          <t>변경된 문장 없음</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -2751,602 +3122,8 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>목록 진입</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>응답 시간은 1.2ms로 변화 없음</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>이전 실행에서는 목록에 없었음 (이전 X)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>목록 이탈</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>이전 C → 현재 X</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>목록 이탈</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>사내 조립 공정 표준 개정 추진</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>이전 C → 현재 X</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>등급 변경</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>B → C</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>등급 변경</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>연산량 증가는 기존 MCU 사이클 내에서 수용 가능</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>A → B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>응력이 피에조 저항 브리지의 불균형을 유발하여 오프셋 변화로 나타남</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.72 → 0.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>접착제 두께 편차(±15㎛)가 클수록 드리프트가 커지는 경향 확인</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.72 → 0.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>다이 하부에 응력 완충용 더미 층(폴리이미드 25㎛) 삽입</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>접착제 도포량 자동 제어로 두께 편차 ±5㎛ 이내 관리</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>펌웨어에서 온도별 오프셋을 2차 다항식으로 보정</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>보정 계수는 모듈별로 OTP 메모리에 저장하고 부팅 시 로드</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>85℃ 500시간 시험에서 오프셋 드리프트 0.35%FS → 0.10%FS (약 70% 감소)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.81 → 0.58</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>항목: 조립 수율 | 개선 전: 92.1 % | 개선 후: 97.8 %</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.81 → 0.69</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>차기 모델 PS-300에 자체 개발 온도 보정 IP 적용 예정</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.68 → 0.53</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I18"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3506,6 +3283,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>섹션</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>페이지</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>줄</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>발췌</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>논의 포인트</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>점수</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>1차 분류기</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2차 LLM</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>배경 및 문제점</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>향후 계획</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>사내 조립 공정 표준 개정 추진</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O3"/>
+  <dataValidations count="1">
+    <dataValidation sqref="N2:N3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+      <formula1>"O,X,A,B,C,D"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3545,7 +3538,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20261027-195017-samplereport</t>
+          <t>20261027-205729-samplereport</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3550,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>20261027-194955-samplereport</t>
+          <t>20261027-205722-samplereport</t>
         </is>
       </c>
     </row>
@@ -3569,118 +3562,124 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>cascade</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LLM 모델</t>
+          <t>판정 흐름</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>qwen3:4b-instruct</t>
+          <t>분류기 1차 추출(X 제외) → 후보 전부 LLM 2차 판정 → 두 단계 통과만 검토 목록</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>프롬프트 버전</t>
+          <t>단계별 문장 수</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>v5-2026-10-27</t>
+          <t>전체 27 → 1차 제외 2 → 2차 후보 24 → 2차 제외 0 → 보류 1 → 검토 목록 24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>임베딩 모델</t>
+          <t>LLM 모델</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>bge-m3</t>
+          <t>qwen3:4b-instruct</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
+          <t>프롬프트 버전</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>제로샷(원형 문장)</t>
+          <t>v5-2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>확신 임계값</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0.05</v>
+          <t>임베딩 모델</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>bge-m3</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>목록 점수 기준</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0.5</v>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>제로샷(원형 문장)</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>점수 미달 보류</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>0</v>
+          <t>페이지 가중치</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>켬 (관련성 낮음 0.4, 낮음 페이지 0개)</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LLM 재확인 문장</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>목록 점수 기준</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>분류기 채택 문장</t>
+          <t>점수 미달 보류</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LLM 판정 문장</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>8</v>
+          <t>골드 정답 반영</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>없음 (골드 파일이 없거나 use_gold=false)</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3700,7 +3699,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="18">
@@ -3711,7 +3710,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T19:50:17</t>
+          <t>2026-10-27T20:57:29</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3721,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="20">
@@ -3772,7 +3771,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -3793,7 +3792,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>A: 6, B: 8, C: 7, D: 3 (합 24)</t>
+          <t>A: 6, B: 9, C: 6, D: 3 (합 24)</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3804,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>A: 6, B: 8, C: 7, D: 3, X: 2, X?: 1, ?: 0</t>
+          <t>A: 6, B: 9, C: 6, D: 3, X: 2, X?: 1, ?: 0</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3816,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>entered: 1, left: 2, grade: 2, score: 9</t>
+          <t>변경 없음</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3828,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>판정 모드: llm → hybrid; 분류기: - → 제로샷(원형 문장)</t>
+          <t>페이지 가중치 적용: 끔 → 켬</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3864,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>검토 목록·보류·제외 문장 시트의 '피드백' 열에 O=맞음, X=틀림(제외), A/B/C/D=올바른 등급. 저장 후 UI '정확도 관리 → 피드백 가져오기' 또는 ip-finder feedback &lt;이 파일&gt;</t>
+          <t>검토 목록·보류·제외 시트의 '피드백' 열에 O=맞음, X=틀림(제외), A/B/C/D=올바른 등급. 저장 후 UI '정확도 관리 → 피드백 가져오기' 또는 ip-finder feedback &lt;이 파일&gt;</t>
         </is>
       </c>
     </row>

--- a/demo/sample_report_pptx_검토후보.xlsx
+++ b/demo/sample_report_pptx_검토후보.xlsx
@@ -18,15 +18,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실행 정보" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토 목록'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토 목록'!$A$1:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보류'!$A$1:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2차 제외'!$A$1:$O$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'페이지'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'변경 사항'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'변경 사항'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'제외 페이지'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'이미지 페이지'!$A$1:$C$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'1차 제외 (참고)'!$A$1:$O$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'실행 정보'!$A$1:$B$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'1차 제외 (참고)'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'실행 정보'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,22 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCEDC8"/>
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,6 +78,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEDC8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,16 +112,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -595,28 +595,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>배경 및 문제점</t>
+          <t>개선안</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>고온(85℃ 이상) 환경에서 출력 오프셋이 시간에 따라 변하는 드리프트 현상 발생</t>
+          <t>접착제를 저탄성 실리콘계로 변경하여 다이로 전달되는 응력 저감</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -627,12 +627,12 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>분류기 C(0.14)</t>
+          <t>분류기 A(0.01)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr"/>
@@ -654,28 +654,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>배경 및 문제점</t>
+          <t>개선안</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2분기 필드 불량률 1.8%로 목표 0.5% 대비 초과</t>
+          <t>다이 하부에 응력 완충용 더미 층(폴리이미드 25㎛) 삽입</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
+          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -686,12 +686,12 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>분류기 B(0.15)</t>
+          <t>분류기 A(0.08)</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr"/>
@@ -713,28 +713,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>배경 및 문제점</t>
+          <t>개선안</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>기존 보정 방식은 상온 1점 캘리브레이션만 수행하여 온도 변화 대응 불가</t>
+          <t>펌웨어에서 온도별 오프셋을 2차 다항식으로 보정</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -745,12 +745,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>분류기 C(0.31)</t>
+          <t>분류기 A(0.09)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr"/>
@@ -772,28 +772,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>원인 분석</t>
+          <t>개선안</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>다이 어태치 접착제(에폭시계)와 세라믹 기판의 열팽창계수 차이로 고온에서 다이에 응력 발생</t>
+          <t>캘리브레이션 포인트를 1점(25℃)에서 3점(-20/25/85℃)으로 확대</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>분류기 C(0.19)</t>
+          <t>분류기 A(0.03)</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr"/>
@@ -831,28 +831,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>원인 분석</t>
+          <t>개선안</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>응력이 피에조 저항 브리지의 불균형을 유발하여 오프셋 변화로 나타남</t>
+          <t>보정 계수는 모듈별로 OTP 메모리에 저장하고 부팅 시 로드</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -863,12 +863,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>분류기 C(0.08)</t>
+          <t>분류기 A(0.09)</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr"/>
@@ -890,28 +890,28 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>원인 분석</t>
+          <t>개선안</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>접착제 두께 편차(±15㎛)가 클수록 드리프트가 커지는 경향 확인</t>
+          <t>연산량 증가는 기존 MCU 사이클 내에서 수용 가능</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -922,12 +922,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>분류기 C(0.06)</t>
+          <t>분류기 B(0.06)</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr"/>
@@ -949,14 +949,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>원인 분석</t>
+          <t>검증 결과</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
+          <t>85℃ 500시간 시험에서 오프셋 드리프트 0.35%FS → 0.10%FS (약 70% 감소)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>분류기 C(0.02), 불일치</t>
+          <t>분류기 A(0.04), 불일치</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr"/>
@@ -1008,28 +1008,28 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>개선안</t>
+          <t>검증 결과</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>접착제를 저탄성 실리콘계로 변경하여 다이로 전달되는 응력 저감</t>
+          <t>조립 수율 92.1% → 97.8%로 향상</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>분류기 A(0.01)</t>
+          <t>분류기 B(0.15)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr"/>
@@ -1067,28 +1067,28 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>개선안</t>
+          <t>검증 결과</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>3</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>다이 하부에 응력 완충용 더미 층(폴리이미드 25㎛) 삽입</t>
+          <t>응답 시간은 1.2ms로 변화 없음</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>분류기 A(0.08)</t>
+          <t>분류기 B(0.05)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr"/>
@@ -1126,44 +1126,44 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>개선안</t>
+          <t>검증 결과</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>접착제 도포량 자동 제어로 두께 편차 ±5㎛ 이내 관리</t>
+          <t>항목: 오프셋 드리프트 | 개선 전: 0.35 %FS | 개선 후: 0.10 %FS</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>분류기 C(0.00), 불일치</t>
+          <t>표, 분류기 B(0.04)</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr"/>
@@ -1185,28 +1185,28 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>개선안</t>
+          <t>검증 결과</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>펌웨어에서 온도별 오프셋을 2차 다항식으로 보정</t>
+          <t>항목: 조립 수율 | 개선 전: 92.1 % | 개선 후: 97.8 %</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>분류기 A(0.09)</t>
+          <t>표, 분류기 B(0.11)</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr"/>
@@ -1244,28 +1244,28 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>개선안</t>
+          <t>추가 검토 사항</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>3</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>캘리브레이션 포인트를 1점(25℃)에서 3점(-20/25/85℃)으로 확대</t>
+          <t>경쟁사 B 제품 대비 응답 속도 우위(1.2ms vs 2.0ms)는 유지 확인</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
+          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1291,724 +1291,16 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>분류기 A(0.03)</t>
+          <t>분류기 B(0.13)</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr"/>
       <c r="O13" s="4" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>개선안</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>보정 계수는 모듈별로 OTP 메모리에 저장하고 부팅 시 로드</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>분류기 A(0.09)</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>개선안</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>연산량 증가는 기존 MCU 사이클 내에서 수용 가능</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>분류기 B(0.06)</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>검증 결과</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>85℃ 500시간 시험에서 오프셋 드리프트 0.35%FS → 0.10%FS (약 70% 감소)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>분류기 A(0.04), 불일치</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>검증 결과</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>조립 수율 92.1% → 97.8%로 향상</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>분류기 B(0.15)</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>검증 결과</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>응답 시간은 1.2ms로 변화 없음</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>분류기 B(0.05)</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>검증 결과</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>항목: 오프셋 드리프트 | 개선 전: 0.35 %FS | 개선 후: 0.10 %FS</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>표, 분류기 B(0.04)</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>검증 결과</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>항목: 조립 수율 | 개선 전: 92.1 % | 개선 후: 97.8 %</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>표, 분류기 B(0.11)</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>추가 검토 사항</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>전원 노이즈가 큰 일부 고객 설비에서 간헐적 출력 스파이크 관측</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>분류기 C(0.16)</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>추가 검토 사항</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>입력단 필터 구조 변경(RC → LC) 검토 예정</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>변경 내용의 구체적 구성은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>분류기 D(0.16)</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr"/>
-      <c r="O22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>추가 검토 사항</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>경쟁사 B 제품 대비 응답 속도 우위(1.2ms vs 2.0ms)는 유지 확인</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>분류기 B(0.13)</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>향후 계획</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>차기 모델 PS-300에 자체 개발 온도 보정 IP 적용 예정</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>변경 내용의 구체적 구성은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>분류기 D(0.05)</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr"/>
-      <c r="O24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>향후 계획</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>생산 데이터 기반 AI 이상 감지 도입 검토</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>변경 내용의 구체적 구성은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>분류기 D(0.20)</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr"/>
-      <c r="O25" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O25"/>
+  <autoFilter ref="A1:O13"/>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+    <dataValidation sqref="N2:N13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
       <formula1>"O,X,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2140,7 +1432,7 @@
       <c r="D2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>X?</t>
         </is>
@@ -2304,25 +1596,63 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>배경 및 문제점</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>분류기 1차에서 뽑힌 문장 중 LLM 2차가 제외한 문장이 없습니다.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
+          <t>2분기 필드 불량률 1.8%로 목표 0.5% 대비 초과</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>분류기 B(0.15), LLM 2차 제외(C)</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O2"/>
@@ -2547,16 +1877,16 @@
         <v>4</v>
       </c>
       <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -2595,13 +1925,13 @@
         <v>4</v>
       </c>
       <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -2643,13 +1973,13 @@
         <v>3</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -2835,13 +2165,13 @@
         <v>3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -2931,13 +2261,13 @@
         <v>3</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -3008,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3079,7 +2409,7 @@
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>직전 실행 20261027-205722-samplereport 과 비교 (현재 20261027-205729-samplereport)</t>
+          <t>직전 실행 20261027-211528-samplereport 과 비교 (현재 20261027-211540-samplereport)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -3098,7 +2428,7 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>페이지 가중치 적용: 끔 → 켬</t>
+          <t>LLM 모델: qwen3:8b → qwen3:4b-instruct</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -3108,12 +2438,16 @@
       <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>변경된 문장 없음</t>
+          <t>판정 모드: llm → cascade</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -3122,8 +2456,460 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>분류기: - → 제로샷(원형 문장)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>목록 이탈</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2분기 필드 불량률 1.8%로 목표 0.5% 대비 초과</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>이전 B → 현재 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>목록 이탈</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>접착제 도포량 자동 제어로 두께 편차 ±5㎛ 이내 관리</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>이전 A → 현재 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>등급 변경</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>C → X</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>등급 변경</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>사내 조립 공정 표준 개정 추진</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>D → X</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>고온(85℃ 이상) 환경에서 출력 오프셋이 시간에 따라 변하는 드리프트 현상 발생</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>응력이 피에조 저항 브리지의 불균형을 유발하여 오프셋 변화로 나타남</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>접착제 두께 편차(±15㎛)가 클수록 드리프트가 커지는 경향 확인</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>85℃ 500시간 시험에서 오프셋 드리프트 0.35%FS → 0.10%FS (약 70% 감소)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>두 개선안을 모두 적용한 조건의 결과이며 개별 기여도는 별도 분석 예정</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>점수 변경</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>차기 모델 PS-300에 자체 개발 온도 보정 IP 적용 예정</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>점수 0.90 → 0.70</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3283,7 +3069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3393,28 +3179,32 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>고온(85℃ 이상) 환경에서 출력 오프셋이 시간에 따라 변하는 드리프트 현상 발생</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.795</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -3437,11 +3227,11 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>향후 계획</t>
+          <t>배경 및 문제점</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>3</v>
@@ -3453,12 +3243,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>사내 조립 공정 표준 개정 추진</t>
+          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="n">
-        <v>0.758</v>
+        <v>0.9</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -3482,10 +3272,611 @@
       <c r="N3" s="4" t="inlineStr"/>
       <c r="O3" s="4" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>배경 및 문제점</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>기존 보정 방식은 상온 1점 캘리브레이션만 수행하여 온도 변화 대응 불가</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>원인 분석</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>다이 어태치 접착제(에폭시계)와 세라믹 기판의 열팽창계수 차이로 고온에서 다이에 응력 발생</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>원인 분석</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>응력이 피에조 저항 브리지의 불균형을 유발하여 오프셋 변화로 나타남</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>원인 분석</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>접착제 두께 편차(±15㎛)가 클수록 드리프트가 커지는 경향 확인</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>원인 분석</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>개선안</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>접착제 도포량 자동 제어로 두께 편차 ±5㎛ 이내 관리</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>추가 검토 사항</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>전원 노이즈가 큰 일부 고객 설비에서 간헐적 출력 스파이크 관측</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>이 문제의 해결 수단이 있는가, 시도 중인가.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>추가 검토 사항</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>입력단 필터 구조 변경(RC → LC) 검토 예정</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>변경 내용의 구체적 구성은 무엇인가.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>향후 계획</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>차기 모델 PS-300에 자체 개발 온도 보정 IP 적용 예정</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>변경 내용의 구체적 구성은 무엇인가.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>향후 계획</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>생산 데이터 기반 AI 이상 감지 도입 검토</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>변경 내용의 구체적 구성은 무엇인가.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>향후 계획</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>사내 조립 공정 표준 개정 추진</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>분류기</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O3"/>
+  <autoFilter ref="A1:O14"/>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+    <dataValidation sqref="N2:N14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
       <formula1>"O,X,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3499,7 +3890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3538,7 +3929,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20261027-205729-samplereport</t>
+          <t>20261027-211540-samplereport</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3941,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>20261027-205722-samplereport</t>
+          <t>20261027-211528-samplereport</t>
         </is>
       </c>
     </row>
@@ -3569,307 +3960,319 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>판정 흐름</t>
+          <t>추출 등급</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>분류기 1차 추출(X 제외) → 후보 전부 LLM 2차 판정 → 두 단계 통과만 검토 목록</t>
+          <t>A,B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>단계별 문장 수</t>
+          <t>판정 흐름</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>전체 27 → 1차 제외 2 → 2차 후보 24 → 2차 제외 0 → 보류 1 → 검토 목록 24</t>
+          <t>분류기 1차: A,B 로 판정된 문장만 후보 → LLM 2차: 후보가 A,B 인지 판정해 최종 등급 → 두 단계 통과만 검토 목록</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LLM 모델</t>
+          <t>단계별 문장 수</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>qwen3:4b-instruct</t>
+          <t>전체 27 → 1차 제외 13 → 2차 후보 13 → 2차 제외 1 → 보류 1 → 검토 목록 12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>프롬프트 버전</t>
+          <t>LLM 모델</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>v5-2026-10-27</t>
+          <t>qwen3:4b-instruct</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>임베딩 모델</t>
+          <t>프롬프트 버전</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>bge-m3</t>
+          <t>v5-2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>분류기</t>
+          <t>임베딩 모델</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>제로샷(원형 문장)</t>
+          <t>bge-m3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>페이지 가중치</t>
+          <t>분류기</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>켬 (관련성 낮음 0.4, 낮음 페이지 0개)</t>
+          <t>제로샷(원형 문장)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>목록 점수 기준</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.5</v>
+          <t>페이지 가중치</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>켬 (관련성 낮음 0.4, 낮음 페이지 0개)</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>점수 미달 보류</t>
+          <t>목록 점수 기준</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>골드 정답 반영</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>없음 (골드 파일이 없거나 use_gold=false)</t>
-        </is>
+          <t>점수 미달 보류</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>임베딩 시간(초)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>0.5</v>
+          <t>골드 정답 반영</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>없음 (골드 파일이 없거나 use_gold=false)</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LLM 시간(초)</t>
+          <t>임베딩 시간(초)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>시작</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27T20:57:29</t>
-        </is>
+          <t>LLM 시간(초)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>4.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>소요 시간(초)</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>6.9</v>
+          <t>시작</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27T21:15:40</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>페이지 수</t>
+          <t>소요 시간(초)</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>라벨링 페이지</t>
+          <t>페이지 수</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>제외 페이지</t>
+          <t>라벨링 페이지</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>이미지 페이지</t>
+          <t>제외 페이지</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LLM 호출</t>
+          <t>이미지 페이지</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>캐시 적중</t>
+          <t>LLM 호출</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>검토 목록</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>A: 6, B: 9, C: 6, D: 3 (합 24)</t>
-        </is>
+          <t>캐시 적중</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>등급 분포(전체)</t>
+          <t>검토 목록</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>A: 6, B: 9, C: 6, D: 3, X: 2, X?: 1, ?: 0</t>
+          <t>A: 5, B: 7 (합 12)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>직전 실행 대비</t>
+          <t>등급 분포(전체)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>변경 없음</t>
+          <t>A: 5, B: 7, C: 9, D: 3, X: 2, X?: 1, ?: 0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>달라진 설정</t>
+          <t>직전 실행 대비</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>페이지 가중치 적용: 끔 → 켬</t>
+          <t>left: 2, grade: 2, score: 7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>전처리로 제거된 줄</t>
+          <t>달라진 설정</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>숫자만: 1, 반복 문구: 12, 일정/금액: 3, 담당자: 1, 짧은 조각: 1</t>
+          <t>LLM 모델: qwen3:8b → qwen3:4b-instruct; 판정 모드: llm → cascade; 분류기: - → 제로샷(원형 문장)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>경고</t>
+          <t>전처리로 제거된 줄</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>숫자만: 1, 반복 문구: 12, 일정/금액: 3, 담당자: 1, 짧은 조각: 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>경고</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>피드백 방법</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>검토 목록·보류·제외 시트의 '피드백' 열에 O=맞음, X=틀림(제외), A/B/C/D=올바른 등급. 저장 후 UI '정확도 관리 → 피드백 가져오기' 또는 ip-finder feedback &lt;이 파일&gt;</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B32"/>
+  <autoFilter ref="A1:B33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demo/sample_report_pptx_검토후보.xlsx
+++ b/demo/sample_report_pptx_검토후보.xlsx
@@ -18,11 +18,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실행 정보" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토 목록'!$A$1:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'검토 목록'!$A$1:$O$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보류'!$A$1:$P$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2차 제외'!$A$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2차 제외'!$A$1:$O$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'페이지'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'변경 사항'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'변경 사항'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'제외 페이지'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'이미지 페이지'!$A$1:$C$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'1차 제외 (참고)'!$A$1:$O$14</definedName>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -899,35 +899,35 @@
       <c r="D7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>연산량 증가는 기존 MCU 사이클 내에서 수용 가능</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>기존 방식과 무엇이 다른가. 변형 가능한 범위는.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>연산량 증가는 기존 MCU 사이클 내에서 수용 가능</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>분류기 B(0.06)</t>
+          <t>분류기 B(0.06), 불일치</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>응답 시간은 1.2ms로 변화 없음</t>
+          <t>항목: 오프셋 드리프트 | 개선 전: 0.35 %FS | 개선 후: 0.10 %FS</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>분류기 B(0.05)</t>
+          <t>표, 분류기 B(0.04)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>항목: 오프셋 드리프트 | 개선 전: 0.35 %FS | 개선 후: 0.10 %FS</t>
+          <t>항목: 조립 수율 | 개선 전: 92.1 % | 개선 후: 97.8 %</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>표, 분류기 B(0.04)</t>
+          <t>표, 분류기 B(0.11)</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr"/>
@@ -1185,14 +1185,14 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>검증 결과</t>
+          <t>추가 검토 사항</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>항목: 조립 수율 | 개선 전: 92.1 % | 개선 후: 97.8 %</t>
+          <t>경쟁사 B 제품 대비 응답 속도 우위(1.2ms vs 2.0ms)는 유지 확인</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1232,75 +1232,16 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>표, 분류기 B(0.11)</t>
+          <t>분류기 B(0.13)</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr"/>
       <c r="O12" s="4" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>추가 검토 사항</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>경쟁사 B 제품 대비 응답 속도 우위(1.2ms vs 2.0ms)는 유지 확인</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>이 효과를 얻은 구체적 수단은 무엇인가.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>분류기 B(0.13)</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O13"/>
+  <autoFilter ref="A1:O12"/>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+    <dataValidation sqref="N2:N12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
       <formula1>"O,X,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1498,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1654,10 +1595,65 @@
       <c r="N2" s="4" t="inlineStr"/>
       <c r="O2" s="4" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>검증 결과</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>응답 시간은 1.2ms로 변화 없음</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>분류기 B(0.05), LLM 2차 제외(X)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:O3"/>
   <dataValidations count="1">
-    <dataValidation sqref="N2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
+    <dataValidation sqref="N2:N3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="피드백" prompt="O=맞음, X=틀림(제외), A/B/C/D=올바른 등급" type="list">
       <formula1>"O,X,A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2117,7 +2113,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>1</v>
@@ -2126,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -2338,7 +2334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2400,16 +2396,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>기준</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>직전 실행 20261027-211528-samplereport 과 비교 (현재 20261027-211540-samplereport)</t>
+          <t>이 파일의 이전 실행 기록이 없어 비교하지 않았습니다. 다음 실행부터 여기에 달라진 행이 적힙니다.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -2418,498 +2410,8 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>LLM 모델: qwen3:8b → qwen3:4b-instruct</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>판정 모드: llm → cascade</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>분류기: - → 제로샷(원형 문장)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>목록 이탈</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2분기 필드 불량률 1.8%로 목표 0.5% 대비 초과</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>이전 B → 현재 C</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>목록 이탈</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>접착제 도포량 자동 제어로 두께 편차 ±5㎛ 이내 관리</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>이전 A → 현재 C</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>등급 변경</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>주요 고객 A사 클레임 3건 접수, 11월까지 대응 방안 회신 요청</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>C → X</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>등급 변경</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>사내 조립 공정 표준 개정 추진</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>D → X</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>고온(85℃ 이상) 환경에서 출력 오프셋이 시간에 따라 변하는 드리프트 현상 발생</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>응력이 피에조 저항 브리지의 불균형을 유발하여 오프셋 변화로 나타남</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>접착제 두께 편차(±15㎛)가 클수록 드리프트가 커지는 경향 확인</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>전원 리플의 영향도 일부 있으나 기여도는 10% 미만으로 추정</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>85℃ 500시간 시험에서 오프셋 드리프트 0.35%FS → 0.10%FS (약 70% 감소)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>두 개선안을 모두 적용한 조건의 결과이며 개별 기여도는 별도 분석 예정</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>점수 변경</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>차기 모델 PS-300에 자체 개발 온도 보정 IP 적용 예정</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>분류기</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>점수 0.90 → 0.70</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3929,7 +3431,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20261027-211540-samplereport</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3443,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>20261027-211528-samplereport</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3491,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>전체 27 → 1차 제외 13 → 2차 후보 13 → 2차 제외 1 → 보류 1 → 검토 목록 12</t>
+          <t>전체 27 → 1차 제외 13 → 2차 후보 13 → 2차 제외 2 → 보류 1 → 검토 목록 11</t>
         </is>
       </c>
     </row>
@@ -4113,7 +3615,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27T21:15:40</t>
+          <t>2026-10-27T21:42:46</t>
         </is>
       </c>
     </row>
@@ -4174,7 +3676,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -4195,7 +3697,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>A: 5, B: 7 (합 12)</t>
+          <t>A: 6, B: 5 (합 11)</t>
         </is>
       </c>
     </row>
@@ -4207,7 +3709,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>A: 5, B: 7, C: 9, D: 3, X: 2, X?: 1, ?: 0</t>
+          <t>A: 6, B: 5, C: 9, D: 3, X: 3, X?: 1, ?: 0</t>
         </is>
       </c>
     </row>
@@ -4219,7 +3721,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>left: 2, grade: 2, score: 7</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4231,7 +3733,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LLM 모델: qwen3:8b → qwen3:4b-instruct; 판정 모드: llm → cascade; 분류기: - → 제로샷(원형 문장)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
